--- a/data/trans_camb/P2A_ner_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 8,62</t>
+          <t>-0,49; 8,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 7,94</t>
+          <t>-0,0; 8,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 6,92</t>
+          <t>0,04; 6,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 2,26</t>
+          <t>-3,52; 2,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 10,24</t>
+          <t>0,14; 10,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 3,53</t>
+          <t>-3,52; 3,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,84</t>
+          <t>-1,56; 3,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,7</t>
+          <t>0,85; 7,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,08</t>
+          <t>-0,73; 3,76</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 2099,2</t>
+          <t>1,29; 1672,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-46,88; 992,2</t>
+          <t>-63,37; 999,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 2,07</t>
+          <t>-7,76; 1,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 5,7</t>
+          <t>-5,09; 6,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 4,4</t>
+          <t>-5,61; 5,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 1,0</t>
+          <t>-6,64; 1,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 2,79</t>
+          <t>-5,04; 3,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 7,21</t>
+          <t>-3,15; 7,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 0,4</t>
+          <t>-5,93; 0,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,91</t>
+          <t>-3,4; 3,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,7</t>
+          <t>-2,76; 4,35</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-78,26; 534,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-83,24; 340,19</t>
+          <t>-88,14; 602,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>-100,0; 357,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,07; 701,09</t>
+          <t>-73,2; 638,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 63,57</t>
+          <t>-100,0; 54,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,42; 179,75</t>
+          <t>-68,21; 181,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,63; 251,65</t>
+          <t>-57,14; 212,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,78</t>
+          <t>1,14; 9,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,2</t>
+          <t>1,22; 9,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,27; 17,78</t>
+          <t>3,49; 17,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 1,16</t>
+          <t>-5,51; 1,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 3,8</t>
+          <t>-4,42; 3,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 10,59</t>
+          <t>-1,66; 11,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,87</t>
+          <t>-1,57; 4,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,72</t>
+          <t>-1,06; 4,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 11,5</t>
+          <t>1,97; 11,49</t>
         </is>
       </c>
     </row>
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-90,19; —</t>
+          <t>-66,58; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,1; 787,4</t>
+          <t>-80,73; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-72,86; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,81; 2366,71</t>
+          <t>27,5; 2134,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 2,1</t>
+          <t>-3,75; 2,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 4,39</t>
+          <t>-2,21; 4,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 2,73</t>
+          <t>-2,95; 2,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,36</t>
+          <t>-2,99; 1,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,94</t>
+          <t>0,51; 6,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,76</t>
+          <t>0,66; 7,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,79</t>
+          <t>-2,46; 0,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,29</t>
+          <t>0,23; 4,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 4,09</t>
+          <t>-0,28; 4,0</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-86,51; 186,98</t>
+          <t>-84,45; 166,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-50,17; 273,56</t>
+          <t>-49,94; 298,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,26; 183,61</t>
+          <t>-66,79; 197,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 1356,25</t>
+          <t>-25,27; 1278,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 1299,65</t>
+          <t>-9,25; 1326,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-82,64; 79,48</t>
+          <t>-78,23; 95,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 324,81</t>
+          <t>2,74; 379,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 322,95</t>
+          <t>-10,36; 316,23</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 7,05</t>
+          <t>-0,34; 7,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 11,31</t>
+          <t>1,9; 11,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,87; 11,58</t>
+          <t>2,7; 11,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 0,98</t>
+          <t>-8,89; 0,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 6,39</t>
+          <t>-4,62; 6,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 7,75</t>
+          <t>-3,8; 7,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 2,78</t>
+          <t>-3,53; 2,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 7,59</t>
+          <t>-0,66; 7,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 7,73</t>
+          <t>0,73; 7,78</t>
         </is>
       </c>
     </row>
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 75,24</t>
+          <t>-100,0; 128,65</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-63,43; 244,42</t>
+          <t>-57,8; 254,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-41,57; 275,42</t>
+          <t>-44,99; 244,61</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-68,96; 174,68</t>
+          <t>-69,92; 155,58</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 398,14</t>
+          <t>-22,67; 357,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1,3; 447,2</t>
+          <t>7,21; 465,37</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 5,2</t>
+          <t>-5,12; 5,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 11,28</t>
+          <t>-1,48; 11,16</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 13,67</t>
+          <t>-0,31; 13,94</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 3,88</t>
+          <t>-4,55; 3,84</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 9,0</t>
+          <t>-1,36; 9,78</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,07; 14,88</t>
+          <t>0,46; 14,19</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 2,8</t>
+          <t>-3,8; 2,53</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 8,08</t>
+          <t>-0,27; 7,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,73; 11,32</t>
+          <t>1,54; 11,19</t>
         </is>
       </c>
     </row>
@@ -1868,42 +1868,42 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-52,21; 983,04</t>
+          <t>-48,85; 1043,78</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-37,59; 843,0</t>
+          <t>-35,86; 1118,61</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-83,91; 1077,82</t>
+          <t>-58,37; 1153,55</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 1452,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-79,87; 228,17</t>
+          <t>-84,79; 184,49</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 564,66</t>
+          <t>-20,66; 422,26</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>17,26; 666,98</t>
+          <t>24,97; 697,31</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,61</t>
+          <t>-0,78; 2,49</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,58</t>
+          <t>1,12; 4,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,78</t>
+          <t>1,21; 4,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,08</t>
+          <t>-2,71; 0,11</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,93</t>
+          <t>0,33; 3,82</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,98</t>
+          <t>0,96; 4,83</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,69</t>
+          <t>-1,47; 0,7</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,67</t>
+          <t>1,05; 3,75</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,34</t>
+          <t>1,6; 4,31</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-28,83; 183,26</t>
+          <t>-27,51; 159,34</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>32,78; 296,39</t>
+          <t>32,58; 314,93</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>36,85; 331,15</t>
+          <t>29,29; 316,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-77,75; 8,39</t>
+          <t>-78,16; 11,87</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,87; 201,58</t>
+          <t>8,36; 199,54</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,95; 256,48</t>
+          <t>27,3; 246,25</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-47,44; 35,21</t>
+          <t>-49,18; 36,2</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>36,72; 187,95</t>
+          <t>33,55; 193,84</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>49,19; 221,28</t>
+          <t>50,35; 226,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 8,56</t>
+          <t>-0,82; 8,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 8,68</t>
+          <t>0,0; 8,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,75</t>
+          <t>-0,11; 6,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 2,22</t>
+          <t>-3,31; 2,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 10,63</t>
+          <t>0,03; 10,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 3,48</t>
+          <t>-3,02; 2,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,77</t>
+          <t>-1,18; 4,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,77</t>
+          <t>0,87; 8,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,76</t>
+          <t>-0,74; 3,68</t>
         </is>
       </c>
     </row>
@@ -803,27 +803,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>-67,72; —</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,2; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1672,01</t>
+          <t>1,15; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-63,37; 999,32</t>
+          <t>-47,72; —</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 1,94</t>
+          <t>-6,73; 1,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 6,29</t>
+          <t>-5,06; 6,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 5,37</t>
+          <t>-5,11; 5,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 1,06</t>
+          <t>-6,65; 1,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 3,34</t>
+          <t>-5,51; 3,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 7,32</t>
+          <t>-3,35; 6,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 0,4</t>
+          <t>-5,5; 0,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 3,26</t>
+          <t>-3,57; 2,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 4,35</t>
+          <t>-2,68; 4,8</t>
         </is>
       </c>
     </row>
@@ -1004,42 +1004,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>-84,39; 488,14</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>-81,91; 490,04</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-88,14; 602,49</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 357,47</t>
+          <t>-100,0; 592,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,2; 638,1</t>
+          <t>-65,48; 734,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 54,15</t>
+          <t>-100,0; 64,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,21; 181,92</t>
+          <t>-68,19; 151,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-57,14; 212,0</t>
+          <t>-47,32; 292,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 9,91</t>
+          <t>1,15; 10,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 9,99</t>
+          <t>1,21; 10,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,49; 17,76</t>
+          <t>4,24; 19,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 1,28</t>
+          <t>-5,75; 1,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 3,62</t>
+          <t>-4,29; 4,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 11,51</t>
+          <t>-1,8; 10,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 4,26</t>
+          <t>-1,48; 4,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 4,81</t>
+          <t>-1,4; 4,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 11,49</t>
+          <t>1,97; 11,08</t>
         </is>
       </c>
     </row>
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,58; —</t>
+          <t>-76,51; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-80,73; —</t>
+          <t>-75,99; 879,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,86; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,5; 2134,25</t>
+          <t>37,83; 2115,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 2,03</t>
+          <t>-4,04; 2,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 4,55</t>
+          <t>-1,89; 4,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,91</t>
+          <t>-2,81; 2,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,32</t>
+          <t>-3,08; 1,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,54</t>
+          <t>0,69; 6,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 7,07</t>
+          <t>0,72; 6,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,86</t>
+          <t>-2,78; 0,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,64</t>
+          <t>-0,16; 4,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,0</t>
+          <t>-0,53; 4,12</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,45; 166,52</t>
+          <t>-90,76; 169,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,94; 298,03</t>
+          <t>-45,5; 284,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-66,79; 197,24</t>
+          <t>-61,87; 236,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,27; 1278,29</t>
+          <t>0,31; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 1326,89</t>
+          <t>-2,81; 1447,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-78,23; 95,25</t>
+          <t>-82,51; 94,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,74; 379,82</t>
+          <t>-8,6; 342,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 316,23</t>
+          <t>-20,37; 308,36</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 7,36</t>
+          <t>-0,44; 7,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,9; 11,36</t>
+          <t>2,65; 11,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,7; 11,02</t>
+          <t>2,45; 11,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 0,94</t>
+          <t>-8,28; 1,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 6,42</t>
+          <t>-5,01; 6,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 7,23</t>
+          <t>-3,29; 7,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 2,68</t>
+          <t>-4,03; 2,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 7,18</t>
+          <t>-0,29; 7,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,78</t>
+          <t>0,5; 7,98</t>
         </is>
       </c>
     </row>
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 128,65</t>
+          <t>-100,0; 88,98</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-57,8; 254,19</t>
+          <t>-63,26; 251,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-44,99; 244,61</t>
+          <t>-42,48; 276,07</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-69,92; 155,58</t>
+          <t>-75,97; 135,74</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-22,67; 357,51</t>
+          <t>-12,97; 377,73</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>7,21; 465,37</t>
+          <t>-4,35; 447,15</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 5,61</t>
+          <t>-5,1; 5,49</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 11,16</t>
+          <t>-1,73; 11,09</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 13,94</t>
+          <t>-0,0; 12,81</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 3,84</t>
+          <t>-4,93; 3,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 9,78</t>
+          <t>-1,62; 8,52</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,46; 14,19</t>
+          <t>1,1; 14,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,53</t>
+          <t>-3,51; 3,02</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 7,9</t>
+          <t>-0,23; 8,14</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,54; 11,19</t>
+          <t>1,68; 10,94</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-48,85; 1043,78</t>
+          <t>-56,01; 774,9</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 1118,61</t>
+          <t>-36,93; 1161,67</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1883,27 +1883,27 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-58,37; 1153,55</t>
+          <t>-54,91; 992,44</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-20,83; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-84,79; 184,49</t>
+          <t>-78,55; 236,8</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 422,26</t>
+          <t>-15,21; 454,83</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>24,97; 697,31</t>
+          <t>18,87; 711,71</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,49</t>
+          <t>-0,77; 2,52</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,77</t>
+          <t>1,18; 4,87</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,96</t>
+          <t>1,26; 4,86</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,11</t>
+          <t>-2,79; 0,04</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,82</t>
+          <t>0,28; 4,15</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,83</t>
+          <t>1,0; 4,71</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,7</t>
+          <t>-1,32; 0,77</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,75</t>
+          <t>1,3; 4,0</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,31</t>
+          <t>1,63; 4,24</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 159,34</t>
+          <t>-27,83; 163,41</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>32,58; 314,93</t>
+          <t>35,95; 326,84</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29,29; 316,47</t>
+          <t>36,17; 300,0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-78,16; 11,87</t>
+          <t>-76,58; 7,73</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>8,36; 199,54</t>
+          <t>6,36; 214,73</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,3; 246,25</t>
+          <t>24,85; 244,48</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 36,2</t>
+          <t>-44,05; 43,03</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>33,55; 193,84</t>
+          <t>41,94; 208,2</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>50,35; 226,05</t>
+          <t>51,54; 219,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,55</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,73</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,99</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,05</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,37</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>3,42</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>1,91</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 8,49</t>
+          <t>-3,51; 2,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,5</t>
+          <t>0,1; 10,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 6,97</t>
+          <t>-2,64; 4,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,33</t>
+          <t>-0,53; 8,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 10,59</t>
+          <t>-0,42; 7,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 2,98</t>
+          <t>0,35; 7,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,05</t>
+          <t>-1,27; 3,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,01</t>
+          <t>0,92; 7,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,68</t>
+          <t>-0,38; 4,75</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-39,93%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>266,94%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>33,32%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>326,9%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>358,4%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>365,23%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-39,93%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>266,94%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>409,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>123,94%</t>
+          <t>157,92%</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,72; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-78,2; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,15; —</t>
+          <t>2,27; 2099,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,72; —</t>
+          <t>-39,71; 1158,54</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,35</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,87</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,67</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,41</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 1,98</t>
+          <t>-6,38; 1,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 6,02</t>
+          <t>-5,41; 2,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 5,46</t>
+          <t>-3,1; 7,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 1,21</t>
+          <t>-7,7; 2,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 3,37</t>
+          <t>-4,86; 5,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 6,76</t>
+          <t>-5,2; 4,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 0,59</t>
+          <t>-5,56; 0,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 2,75</t>
+          <t>-3,48; 2,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 4,8</t>
+          <t>-2,6; 4,67</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-70,52%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-26,14%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>50,11%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-50,15%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>10,6%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-70,52%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-26,14%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-84,39; 488,14</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-81,91; 490,04</t>
+          <t>-70,44; 719,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 592,59</t>
+          <t>-78,26; 534,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,48; 734,27</t>
+          <t>-83,1; 352,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 64,23</t>
+          <t>-100,0; 63,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,19; 151,21</t>
+          <t>-67,42; 179,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,32; 292,29</t>
+          <t>-56,66; 246,54</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,64</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,42</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,94</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,4</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>3,76</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9,21</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,64</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,42</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>10,31</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,0</t>
+          <t>6,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,21</t>
+          <t>-5,74; 1,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,11</t>
+          <t>-4,33; 3,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 19,49</t>
+          <t>-1,71; 12,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 1,22</t>
+          <t>1,07; 10,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 4,46</t>
+          <t>1,22; 11,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 10,73</t>
+          <t>4,74; 19,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,17</t>
+          <t>-1,56; 3,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,85</t>
+          <t>-1,32; 4,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 11,08</t>
+          <t>2,26; 12,54</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-63,19%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-16,09%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>152,12%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-63,19%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-16,09%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>138,0%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>73,95%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>392,52%</t>
+          <t>446,83%</t>
         </is>
       </c>
     </row>
@@ -1225,27 +1225,27 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>-97,33; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-76,51; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-75,99; 879,72</t>
+          <t>-81,1; 787,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37,83; 2115,54</t>
+          <t>15,91; 2551,15</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,56</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,17</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,34</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>2,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,05</t>
+          <t>-2,95; 1,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 4,29</t>
+          <t>0,56; 6,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,97</t>
+          <t>0,91; 7,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,34</t>
+          <t>-3,86; 2,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,78</t>
+          <t>-1,9; 4,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,93</t>
+          <t>-2,43; 3,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,94</t>
+          <t>-2,74; 0,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,54</t>
+          <t>0,16; 4,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,12</t>
+          <t>0,25; 4,71</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-37,62%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>226,27%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>277,98%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-33,54%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>39,3%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-37,62%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>226,27%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>256,93%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>109,17%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-90,76; 169,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,5; 284,5</t>
+          <t>-27,34; 1356,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,87; 236,41</t>
+          <t>-5,09; 1372,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,51; 186,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,31; —</t>
+          <t>-50,17; 273,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1447,44</t>
+          <t>-58,96; 238,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-82,51; 94,39</t>
+          <t>-82,64; 79,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 342,6</t>
+          <t>-2,53; 324,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 308,36</t>
+          <t>3,04; 371,45</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-3,31</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,97</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,48</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,91</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>6,25</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>6,58</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-3,31</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,97</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,35</t>
+          <t>6,66</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>4,36</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 7,35</t>
+          <t>-8,35; 0,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,65; 11,61</t>
+          <t>-5,04; 6,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,45; 11,25</t>
+          <t>-3,25; 8,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 1,13</t>
+          <t>-0,32; 7,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 6,22</t>
+          <t>2,26; 11,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 7,7</t>
+          <t>2,9; 11,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,32</t>
+          <t>-3,76; 2,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 7,01</t>
+          <t>-0,18; 7,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 7,98</t>
+          <t>0,43; 7,97</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-59,82%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>17,45%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>44,8%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>318,23%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>683,08%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>719,65%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-59,82%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>727,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>123,38%</t>
+          <t>126,14%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 75,24</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>-63,43; 244,42</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>-42,01; 285,66</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 88,98</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>-63,26; 251,3</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-42,48; 276,07</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-75,97; 135,74</t>
+          <t>-68,96; 174,68</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 377,73</t>
+          <t>-14,11; 398,14</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 447,15</t>
+          <t>-2,19; 461,94</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3,29</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>6,9</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-0,52</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>3,7</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>5,48</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3,29</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,33</t>
+          <t>5,46</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>6,17</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 5,49</t>
+          <t>-4,54; 3,88</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 11,09</t>
+          <t>-1,73; 9,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 12,81</t>
+          <t>0,42; 16,11</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 3,68</t>
+          <t>-4,54; 5,2</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 8,52</t>
+          <t>-1,75; 11,28</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,1; 14,49</t>
+          <t>-0,44; 13,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 3,02</t>
+          <t>-3,59; 2,8</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 8,14</t>
+          <t>-0,58; 8,08</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,68; 10,94</t>
+          <t>1,92; 11,65</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-9,86%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>120,61%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>252,71%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-15,41%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>110,19%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>163,22%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-9,86%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>120,61%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>231,6%</t>
+          <t>162,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>193,47%</t>
+          <t>202,26%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>-83,91; 1077,82</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>-34,06; 1525,74</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>-56,01; 774,9</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>-36,93; 1161,67</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-54,91; 992,44</t>
+          <t>-52,21; 983,04</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-20,83; —</t>
+          <t>-40,64; 893,47</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-78,55; 236,8</t>
+          <t>-79,87; 228,17</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 454,83</t>
+          <t>-21,31; 564,66</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>18,87; 711,71</t>
+          <t>21,55; 690,98</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2,02</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3,17</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,79</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2,83</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3,04</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>2,02</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>3,52</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>3,34</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,52</t>
+          <t>-2,8; 0,08</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,87</t>
+          <t>0,28; 3,93</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,86</t>
+          <t>1,37; 5,35</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,04</t>
+          <t>-0,78; 2,61</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,15</t>
+          <t>1,11; 4,58</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,71</t>
+          <t>1,62; 5,41</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,77</t>
+          <t>-1,42; 0,69</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,0</t>
+          <t>1,2; 3,67</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,24</t>
+          <t>1,96; 4,75</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-49,62%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>73,78%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>115,99%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>35,91%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>129,24%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>138,92%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-49,62%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>73,78%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>105,87%</t>
+          <t>160,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>120,48%</t>
+          <t>135,43%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-27,83; 163,41</t>
+          <t>-77,75; 8,39</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>35,95; 326,84</t>
+          <t>3,87; 201,58</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>36,17; 300,0</t>
+          <t>35,31; 273,06</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-76,58; 7,73</t>
+          <t>-28,83; 183,26</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6,36; 214,73</t>
+          <t>32,78; 296,39</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>24,85; 244,48</t>
+          <t>51,18; 362,78</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-44,05; 43,03</t>
+          <t>-47,44; 35,21</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>41,94; 208,2</t>
+          <t>36,72; 187,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>51,54; 219,75</t>
+          <t>63,48; 248,55</t>
         </is>
       </c>
     </row>
